--- a/nr/NR_sammenhenger.xlsx
+++ b/nr/NR_sammenhenger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ssbno-my.sharepoint.com/personal/thb_ssb_no/Documents/Infografikk arbeidsmappe/_Seksjon 702/NR/Nr ws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="1_{C5C1F706-3044-4F05-A798-4088D00B8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D389BCD-4D25-45CE-A8CB-DB250A87C824}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="1_{C5C1F706-3044-4F05-A798-4088D00B8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DF067EC-75F0-43E0-864E-D3A0703F30C1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9063F859-FFB0-4ECD-8E4A-53A11DB5693E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{9063F859-FFB0-4ECD-8E4A-53A11DB5693E}"/>
   </bookViews>
   <sheets>
     <sheet name="TO DO" sheetId="3" r:id="rId1"/>
@@ -672,15 +672,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B3D0B8-2838-4235-A4EE-3F9BDDF494A4}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="19.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="15.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>32</v>
       </c>
@@ -691,7 +691,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -702,7 +702,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -713,7 +713,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -724,7 +724,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -735,7 +735,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -746,7 +746,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -757,7 +757,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -768,7 +768,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -779,7 +779,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -790,7 +790,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -801,7 +801,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
@@ -817,20 +817,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}">
   <dimension ref="A1:I196"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="19.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="16.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="16.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="16.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" style="1"/>
     <col min="7" max="7" width="7" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.54296875" style="1" customWidth="1"/>
     <col min="9" max="9" width="28" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="11.42578125" style="1"/>
+    <col min="10" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -859,7 +859,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,7 +886,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -913,7 +913,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -940,7 +940,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -965,7 +965,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -990,7 +990,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="H31" s="11"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="H32" s="11"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="H33" s="11"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="H34" s="11"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="H35" s="11"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H36" s="11"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A37" s="1" t="s">
         <v>6</v>
       </c>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H38" s="11"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A39" s="1" t="s">
         <v>6</v>
       </c>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="H39" s="11"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="H40" s="11"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A41" s="1" t="s">
         <v>6</v>
       </c>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H41" s="11"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A42" s="1" t="s">
         <v>6</v>
       </c>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H42" s="11"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="H43" s="11"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H44" s="11"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A45" s="1" t="s">
         <v>6</v>
       </c>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H45" s="11"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="H46" s="11"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A47" s="1" t="s">
         <v>15</v>
       </c>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="H47" s="11"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A48" s="1" t="s">
         <v>15</v>
       </c>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A49" s="1" t="s">
         <v>5</v>
       </c>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="H49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="H51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A53" s="1" t="s">
         <v>8</v>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="H53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A54" s="1" t="s">
         <v>8</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A55" s="1" t="s">
         <v>9</v>
       </c>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="H55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A56" s="1" t="s">
         <v>9</v>
       </c>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="H56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A57" s="1" t="s">
         <v>9</v>
       </c>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="H57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A58" s="1" t="s">
         <v>9</v>
       </c>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A59" s="1" t="s">
         <v>9</v>
       </c>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A60" s="1" t="s">
         <v>10</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A61" s="1" t="s">
         <v>10</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A62" s="1" t="s">
         <v>10</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A64" s="1" t="s">
         <v>10</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A65" s="1" t="s">
         <v>10</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A66" s="1" t="s">
         <v>10</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A67" s="1" t="s">
         <v>10</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A68" s="1" t="s">
         <v>10</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A69" s="1" t="s">
         <v>10</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A70" s="1" t="s">
         <v>11</v>
       </c>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="H70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A72" s="1" t="s">
         <v>11</v>
       </c>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="H72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A73" s="1" t="s">
         <v>11</v>
       </c>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="H75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A76" s="1" t="s">
         <v>11</v>
       </c>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="H76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A77" s="1" t="s">
         <v>11</v>
       </c>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="H77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A78" s="1" t="s">
         <v>11</v>
       </c>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A79" s="1" t="s">
         <v>11</v>
       </c>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="H79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A80" s="1" t="s">
         <v>11</v>
       </c>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="H80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A81" s="1" t="s">
         <v>11</v>
       </c>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A82" s="1" t="s">
         <v>11</v>
       </c>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="H82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A83" s="1" t="s">
         <v>11</v>
       </c>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="H83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A84" s="1" t="s">
         <v>11</v>
       </c>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="H84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A85" s="1" t="s">
         <v>11</v>
       </c>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A86" s="1" t="s">
         <v>11</v>
       </c>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="H86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A87" s="1" t="s">
         <v>11</v>
       </c>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A88" s="1" t="s">
         <v>11</v>
       </c>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="H88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A89" s="1" t="s">
         <v>11</v>
       </c>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="H89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A90" s="1" t="s">
         <v>11</v>
       </c>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="H90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A91" s="1" t="s">
         <v>12</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A92" s="1" t="s">
         <v>12</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A93" s="1" t="s">
         <v>12</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A94" s="1" t="s">
         <v>12</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A95" s="1" t="s">
         <v>12</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A96" s="1" t="s">
         <v>12</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A97" s="1" t="s">
         <v>12</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A98" s="1" t="s">
         <v>12</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A99" s="1" t="s">
         <v>12</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A100" s="1" t="s">
         <v>12</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A101" s="1" t="s">
         <v>12</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A102" s="1" t="s">
         <v>16</v>
       </c>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A103" s="1" t="s">
         <v>16</v>
       </c>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A104" s="1" t="s">
         <v>16</v>
       </c>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A105" s="1" t="s">
         <v>16</v>
       </c>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A106" s="1" t="s">
         <v>13</v>
       </c>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A107" s="1" t="s">
         <v>13</v>
       </c>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="H107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A108" s="1" t="s">
         <v>13</v>
       </c>
@@ -3646,9 +3646,9 @@
       </c>
       <c r="H108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A109" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>17</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="H109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A110" s="1" t="s">
         <v>13</v>
       </c>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A111" s="1" t="s">
         <v>13</v>
       </c>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A112" s="1" t="s">
         <v>13</v>
       </c>
@@ -3746,9 +3746,9 @@
       </c>
       <c r="H112" s="11"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A113" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>18</v>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="H113" s="11"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A114" s="1" t="s">
         <v>13</v>
       </c>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="H114" s="11"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A115" s="1" t="s">
         <v>13</v>
       </c>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="H115" s="11"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A116" s="1" t="s">
         <v>13</v>
       </c>
@@ -3846,9 +3846,9 @@
       </c>
       <c r="H116" s="11"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A117" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>19</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="H117" s="11"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A118" s="1" t="s">
         <v>13</v>
       </c>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="H118" s="11"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A119" s="1" t="s">
         <v>13</v>
       </c>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="H119" s="11"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A120" s="1" t="s">
         <v>13</v>
       </c>
@@ -3946,9 +3946,9 @@
       </c>
       <c r="H120" s="11"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A121" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>20</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="H121" s="11"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A122" s="1" t="s">
         <v>13</v>
       </c>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="H122" s="11"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A123" s="1" t="s">
         <v>13</v>
       </c>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="H123" s="11"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A124" s="1" t="s">
         <v>13</v>
       </c>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H124" s="11"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A125" s="1" t="s">
         <v>13</v>
       </c>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="H125" s="11"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A126" s="1" t="s">
         <v>13</v>
       </c>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="H126" s="11"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A127" s="1" t="s">
         <v>13</v>
       </c>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="H127" s="11"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A128" s="1" t="s">
         <v>13</v>
       </c>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A129" s="1" t="s">
         <v>13</v>
       </c>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="H129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A130" s="1" t="s">
         <v>13</v>
       </c>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="H130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A131" s="1" t="s">
         <v>14</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A132" s="1" t="s">
         <v>14</v>
       </c>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="H132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A133" s="1" t="s">
         <v>14</v>
       </c>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A134" s="1" t="s">
         <v>14</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A135" s="1" t="s">
         <v>14</v>
       </c>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="H135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A136" s="1" t="s">
         <v>14</v>
       </c>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="H136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A137" s="1" t="s">
         <v>14</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A138" s="1" t="s">
         <v>14</v>
       </c>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="H138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A139" s="1" t="s">
         <v>14</v>
       </c>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="H139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A140" s="1" t="s">
         <v>14</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A141" s="1" t="s">
         <v>14</v>
       </c>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="H141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A142" s="1" t="s">
         <v>14</v>
       </c>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="H142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A143" s="1" t="s">
         <v>14</v>
       </c>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="H143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.6">
       <c r="F144" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4541,7 +4541,7 @@
       <c r="G144" s="11"/>
       <c r="H144" s="11"/>
     </row>
-    <row r="145" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="145" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F145" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4549,7 +4549,7 @@
       <c r="G145" s="11"/>
       <c r="H145" s="11"/>
     </row>
-    <row r="146" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="146" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F146" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4557,7 +4557,7 @@
       <c r="G146" s="11"/>
       <c r="H146" s="11"/>
     </row>
-    <row r="147" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="147" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F147" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4565,7 +4565,7 @@
       <c r="G147" s="11"/>
       <c r="H147" s="11"/>
     </row>
-    <row r="148" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="148" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F148" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4573,7 +4573,7 @@
       <c r="G148" s="11"/>
       <c r="H148" s="11"/>
     </row>
-    <row r="149" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="149" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F149" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4581,7 +4581,7 @@
       <c r="G149" s="11"/>
       <c r="H149" s="11"/>
     </row>
-    <row r="150" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="150" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F150" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4589,7 +4589,7 @@
       <c r="G150" s="11"/>
       <c r="H150" s="11"/>
     </row>
-    <row r="151" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="151" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F151" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4597,7 +4597,7 @@
       <c r="G151" s="11"/>
       <c r="H151" s="11"/>
     </row>
-    <row r="152" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="152" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F152" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4605,7 +4605,7 @@
       <c r="G152" s="11"/>
       <c r="H152" s="11"/>
     </row>
-    <row r="153" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="153" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F153" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4613,7 +4613,7 @@
       <c r="G153" s="11"/>
       <c r="H153" s="11"/>
     </row>
-    <row r="154" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="154" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F154" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4621,7 +4621,7 @@
       <c r="G154" s="11"/>
       <c r="H154" s="11"/>
     </row>
-    <row r="155" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="155" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F155" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4629,7 +4629,7 @@
       <c r="G155" s="11"/>
       <c r="H155" s="11"/>
     </row>
-    <row r="156" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="156" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F156" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4637,7 +4637,7 @@
       <c r="G156" s="11"/>
       <c r="H156" s="11"/>
     </row>
-    <row r="157" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="157" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F157" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4645,7 +4645,7 @@
       <c r="G157" s="11"/>
       <c r="H157" s="11"/>
     </row>
-    <row r="158" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="158" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F158" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4653,7 +4653,7 @@
       <c r="G158" s="11"/>
       <c r="H158" s="11"/>
     </row>
-    <row r="159" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="159" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F159" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4661,7 +4661,7 @@
       <c r="G159" s="11"/>
       <c r="H159" s="11"/>
     </row>
-    <row r="160" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="160" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F160" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4669,7 +4669,7 @@
       <c r="G160" s="11"/>
       <c r="H160" s="11"/>
     </row>
-    <row r="161" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="161" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F161" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4677,7 +4677,7 @@
       <c r="G161" s="11"/>
       <c r="H161" s="11"/>
     </row>
-    <row r="162" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="162" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F162" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4685,7 +4685,7 @@
       <c r="G162" s="11"/>
       <c r="H162" s="11"/>
     </row>
-    <row r="163" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="163" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F163" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4693,7 +4693,7 @@
       <c r="G163" s="11"/>
       <c r="H163" s="11"/>
     </row>
-    <row r="164" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="164" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F164" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4701,7 +4701,7 @@
       <c r="G164" s="11"/>
       <c r="H164" s="11"/>
     </row>
-    <row r="165" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="165" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F165" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4709,7 +4709,7 @@
       <c r="G165" s="11"/>
       <c r="H165" s="11"/>
     </row>
-    <row r="166" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="166" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F166" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4717,7 +4717,7 @@
       <c r="G166" s="11"/>
       <c r="H166" s="11"/>
     </row>
-    <row r="167" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="167" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F167" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4725,7 +4725,7 @@
       <c r="G167" s="11"/>
       <c r="H167" s="11"/>
     </row>
-    <row r="168" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="168" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F168" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4733,7 +4733,7 @@
       <c r="G168" s="11"/>
       <c r="H168" s="11"/>
     </row>
-    <row r="169" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="169" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F169" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4741,7 +4741,7 @@
       <c r="G169" s="11"/>
       <c r="H169" s="11"/>
     </row>
-    <row r="170" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="170" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F170" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4749,7 +4749,7 @@
       <c r="G170" s="11"/>
       <c r="H170" s="11"/>
     </row>
-    <row r="171" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="171" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F171" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4757,7 +4757,7 @@
       <c r="G171" s="11"/>
       <c r="H171" s="11"/>
     </row>
-    <row r="172" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="172" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F172" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4765,7 +4765,7 @@
       <c r="G172" s="11"/>
       <c r="H172" s="11"/>
     </row>
-    <row r="173" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="173" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F173" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4773,7 +4773,7 @@
       <c r="G173" s="11"/>
       <c r="H173" s="11"/>
     </row>
-    <row r="174" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="174" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F174" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4781,7 +4781,7 @@
       <c r="G174" s="11"/>
       <c r="H174" s="11"/>
     </row>
-    <row r="175" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="175" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F175" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4789,7 +4789,7 @@
       <c r="G175" s="11"/>
       <c r="H175" s="11"/>
     </row>
-    <row r="176" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="176" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F176" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4797,7 +4797,7 @@
       <c r="G176" s="11"/>
       <c r="H176" s="11"/>
     </row>
-    <row r="177" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="177" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F177" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4805,7 +4805,7 @@
       <c r="G177" s="11"/>
       <c r="H177" s="11"/>
     </row>
-    <row r="178" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="178" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F178" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4813,7 +4813,7 @@
       <c r="G178" s="11"/>
       <c r="H178" s="11"/>
     </row>
-    <row r="179" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="179" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F179" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4821,7 +4821,7 @@
       <c r="G179" s="11"/>
       <c r="H179" s="11"/>
     </row>
-    <row r="180" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="180" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F180" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4829,7 +4829,7 @@
       <c r="G180" s="11"/>
       <c r="H180" s="11"/>
     </row>
-    <row r="181" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="181" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F181" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4837,7 +4837,7 @@
       <c r="G181" s="11"/>
       <c r="H181" s="11"/>
     </row>
-    <row r="182" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="182" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F182" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4845,7 +4845,7 @@
       <c r="G182" s="11"/>
       <c r="H182" s="11"/>
     </row>
-    <row r="183" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="183" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F183" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4853,7 +4853,7 @@
       <c r="G183" s="11"/>
       <c r="H183" s="11"/>
     </row>
-    <row r="184" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="184" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F184" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4861,7 +4861,7 @@
       <c r="G184" s="11"/>
       <c r="H184" s="11"/>
     </row>
-    <row r="185" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="185" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F185" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4869,7 +4869,7 @@
       <c r="G185" s="11"/>
       <c r="H185" s="11"/>
     </row>
-    <row r="186" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="186" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F186" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4877,7 +4877,7 @@
       <c r="G186" s="11"/>
       <c r="H186" s="11"/>
     </row>
-    <row r="187" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="187" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F187" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4885,7 +4885,7 @@
       <c r="G187" s="11"/>
       <c r="H187" s="11"/>
     </row>
-    <row r="188" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="188" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F188" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4893,7 +4893,7 @@
       <c r="G188" s="11"/>
       <c r="H188" s="11"/>
     </row>
-    <row r="189" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="189" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F189" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4901,7 +4901,7 @@
       <c r="G189" s="11"/>
       <c r="H189" s="11"/>
     </row>
-    <row r="190" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="190" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F190" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4909,7 +4909,7 @@
       <c r="G190" s="11"/>
       <c r="H190" s="11"/>
     </row>
-    <row r="191" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="191" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F191" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4917,7 +4917,7 @@
       <c r="G191" s="11"/>
       <c r="H191" s="11"/>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="192" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F192" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4925,7 +4925,7 @@
       <c r="G192" s="11"/>
       <c r="H192" s="11"/>
     </row>
-    <row r="193" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="193" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F193" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4933,7 +4933,7 @@
       <c r="G193" s="11"/>
       <c r="H193" s="11"/>
     </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="194" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F194" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4941,7 +4941,7 @@
       <c r="G194" s="11"/>
       <c r="H194" s="11"/>
     </row>
-    <row r="195" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="195" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F195" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4949,7 +4949,7 @@
       <c r="G195" s="11"/>
       <c r="H195" s="11"/>
     </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="196" spans="6:8" x14ac:dyDescent="0.6">
       <c r="F196" s="5" t="str">
         <f t="shared" si="44"/>
         <v>KVARTAL</v>
@@ -4974,7 +4974,7 @@
           <x14:formula1>
             <xm:f>LISTER!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A196 D2:D196</xm:sqref>
+          <xm:sqref>D2:D196 A2:A196</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{424D03F4-B91D-4C98-9865-9386CE07D412}">
           <x14:formula1>
@@ -4997,15 +4997,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4AC0EB3-E901-4261-932E-F1531117BF74}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="19.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="1"/>
+    <col min="4" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A2" s="9" t="s">
         <v>5</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A7" s="9" t="s">
         <v>10</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A9" s="9" t="s">
         <v>12</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A13" s="9" t="s">
         <v>16</v>
       </c>

--- a/nr/NR_sammenhenger.xlsx
+++ b/nr/NR_sammenhenger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ssbno-my.sharepoint.com/personal/thb_ssb_no/Documents/Infografikk arbeidsmappe/_Seksjon 702/NR/Nr ws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="1_{C5C1F706-3044-4F05-A798-4088D00B8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DF067EC-75F0-43E0-864E-D3A0703F30C1}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="1_{C5C1F706-3044-4F05-A798-4088D00B8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{404A288D-A5C9-41D3-A5D1-22018DD8A471}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{9063F859-FFB0-4ECD-8E4A-53A11DB5693E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="LISTER" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SAMMENHENGER!$A$1:$I$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SAMMENHENGER!$A$1:$I$192</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="63">
   <si>
     <t>LEVERANDØR</t>
   </si>
@@ -816,7 +816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}">
-  <dimension ref="A1:I196"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="19.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="16.54296875" style="1" bestFit="1" customWidth="1"/>
@@ -4241,7 +4241,7 @@
         <v>47</v>
       </c>
       <c r="F132" s="5" t="str">
-        <f t="shared" ref="F132:F133" si="39">IF(B132="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F132" si="39">IF(B132="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G132" s="11" t="s">
@@ -4254,25 +4254,28 @@
         <v>14</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F133" s="5" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="F133:F137" si="40">IF(B133="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G133" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H133" s="11"/>
+      <c r="I133" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A134" s="1" t="s">
@@ -4285,66 +4288,66 @@
         <v>19</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F134" s="5" t="str">
-        <f t="shared" ref="F134:F140" si="40">IF(B134="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F134" si="41">IF(B134="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G134" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H134" s="11"/>
-      <c r="I134" s="1" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A135" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F135" s="5" t="str">
-        <f t="shared" ref="F135:F136" si="41">IF(B135="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="40"/>
         <v>KVARTAL</v>
       </c>
       <c r="G135" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H135" s="11"/>
+      <c r="I135" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A136" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F136" s="5" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="F136" si="42">IF(B136="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G136" s="11" t="s">
@@ -4357,10 +4360,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>10</v>
@@ -4385,10 +4388,10 @@
         <v>14</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>11</v>
@@ -4397,7 +4400,7 @@
         <v>47</v>
       </c>
       <c r="F138" s="5" t="str">
-        <f t="shared" ref="F138:F139" si="42">IF(B138="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F138" si="43">IF(B138="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G138" s="11" t="s">
@@ -4410,20 +4413,20 @@
         <v>14</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F139" s="5" t="str">
-        <f t="shared" si="42"/>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F139:F192" si="44">IF(B139="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G139" s="11" t="s">
         <v>51</v>
@@ -4431,106 +4434,35 @@
       <c r="H139" s="11"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A140" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F140" s="5" t="str">
-        <f t="shared" si="40"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G140" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f t="shared" si="44"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G140" s="11"/>
       <c r="H140" s="11"/>
-      <c r="I140" s="1" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A141" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F141" s="5" t="str">
-        <f t="shared" ref="F141:F142" si="43">IF(B141="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G141" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f t="shared" si="44"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G141" s="11"/>
       <c r="H141" s="11"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A142" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F142" s="5" t="str">
-        <f t="shared" si="43"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G142" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f t="shared" si="44"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G142" s="11"/>
       <c r="H142" s="11"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A143" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="F143" s="5" t="str">
-        <f t="shared" ref="F143:F196" si="44">IF(B143="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
-      </c>
-      <c r="G143" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f t="shared" si="44"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G143" s="11"/>
       <c r="H143" s="11"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.6">
@@ -4925,40 +4857,8 @@
       <c r="G192" s="11"/>
       <c r="H192" s="11"/>
     </row>
-    <row r="193" spans="6:8" x14ac:dyDescent="0.6">
-      <c r="F193" s="5" t="str">
-        <f t="shared" si="44"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G193" s="11"/>
-      <c r="H193" s="11"/>
-    </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.6">
-      <c r="F194" s="5" t="str">
-        <f t="shared" si="44"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G194" s="11"/>
-      <c r="H194" s="11"/>
-    </row>
-    <row r="195" spans="6:8" x14ac:dyDescent="0.6">
-      <c r="F195" s="5" t="str">
-        <f t="shared" si="44"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G195" s="11"/>
-      <c r="H195" s="11"/>
-    </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.6">
-      <c r="F196" s="5" t="str">
-        <f t="shared" si="44"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G196" s="11"/>
-      <c r="H196" s="11"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I196" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}"/>
+  <autoFilter ref="A1:I192" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -4968,25 +4868,25 @@
           <x14:formula1>
             <xm:f>LISTER!$B$2:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B196</xm:sqref>
+          <xm:sqref>B2:B192</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4699882C-A539-431A-9F19-F1B3185EADBF}">
           <x14:formula1>
             <xm:f>LISTER!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D196 A2:A196</xm:sqref>
+          <xm:sqref>D2:D192 A2:A192</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{424D03F4-B91D-4C98-9865-9386CE07D412}">
           <x14:formula1>
             <xm:f>LISTER!$C$2:$C$13</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C196</xm:sqref>
+          <xm:sqref>C2:C192</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C0FD7FC9-0A01-4E4D-963C-4616ACB0FCFE}">
           <x14:formula1>
             <xm:f>LISTER!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E196</xm:sqref>
+          <xm:sqref>E2:E192</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/nr/NR_sammenhenger.xlsx
+++ b/nr/NR_sammenhenger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ssbno-my.sharepoint.com/personal/thb_ssb_no/Documents/Infografikk arbeidsmappe/_Seksjon 702/NR/Nr ws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="1_{C5C1F706-3044-4F05-A798-4088D00B8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{404A288D-A5C9-41D3-A5D1-22018DD8A471}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="1_{C5C1F706-3044-4F05-A798-4088D00B8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4087D345-1D7E-4FFC-B341-4E0D840E8049}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{9063F859-FFB0-4ECD-8E4A-53A11DB5693E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9063F859-FFB0-4ECD-8E4A-53A11DB5693E}"/>
   </bookViews>
   <sheets>
     <sheet name="TO DO" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="LISTER" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SAMMENHENGER!$A$1:$I$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SAMMENHENGER!$A$1:$I$193</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="64">
   <si>
     <t>LEVERANDØR</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>DOK</t>
+  </si>
+  <si>
+    <t>1.-2.kv. 24</t>
   </si>
 </sst>
 </file>
@@ -672,15 +675,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B3D0B8-2838-4235-A4EE-3F9BDDF494A4}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="19.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.453125" style="1"/>
+    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>32</v>
       </c>
@@ -691,7 +694,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -702,7 +705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -713,7 +716,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -724,7 +727,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -735,7 +738,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -746,7 +749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -757,7 +760,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -768,7 +771,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -779,7 +782,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -790,7 +793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -801,7 +804,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
@@ -816,21 +819,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}">
-  <dimension ref="A1:I192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="19.5" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:I194"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.453125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.26953125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="16.54296875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" style="1"/>
+    <col min="1" max="1" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="16.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1"/>
     <col min="7" max="7" width="7" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" style="1" customWidth="1"/>
     <col min="9" max="9" width="28" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="11.453125" style="1"/>
+    <col min="10" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -859,7 +862,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,7 +889,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -913,7 +916,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -940,12 +943,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>19</v>
@@ -965,12 +968,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
@@ -990,12 +993,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>19</v>
@@ -1015,12 +1018,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -1040,12 +1043,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -1065,12 +1068,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -1090,12 +1093,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>24</v>
@@ -1115,12 +1118,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>24</v>
@@ -1140,12 +1143,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
@@ -1165,12 +1168,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>24</v>
@@ -1192,12 +1195,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
@@ -1219,12 +1222,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>24</v>
@@ -1246,12 +1249,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>24</v>
@@ -1264,7 +1267,7 @@
       </c>
       <c r="F17" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>KVARTAL</v>
+        <v>ÅR</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>51</v>
@@ -1273,12 +1276,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>25</v>
@@ -1300,12 +1303,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>25</v>
@@ -1327,12 +1330,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>25</v>
@@ -1354,12 +1357,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>25</v>
@@ -1372,7 +1375,7 @@
       </c>
       <c r="F21" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>KVARTAL</v>
+        <v>ÅR</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>51</v>
@@ -1381,12 +1384,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>27</v>
@@ -1408,12 +1411,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>27</v>
@@ -1425,7 +1428,7 @@
         <v>49</v>
       </c>
       <c r="F23" s="5" t="str">
-        <f t="shared" ref="F23:F82" si="3">IF(B23="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F23:F83" si="3">IF(B23="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G23" s="11" t="s">
@@ -1435,12 +1438,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>27</v>
@@ -1462,12 +1465,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>27</v>
@@ -1480,7 +1483,7 @@
       </c>
       <c r="F25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>KVARTAL</v>
+        <v>ÅR</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>51</v>
@@ -1489,7 +1492,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -1516,7 +1519,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1543,12 +1546,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -1561,7 +1564,7 @@
       </c>
       <c r="F28" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>ÅR</v>
+        <v>KVARTAL</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>51</v>
@@ -1570,7 +1573,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -1597,7 +1600,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -1624,32 +1627,34 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F31" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(B31="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H31" s="11"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="H31" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -1660,13 +1665,13 @@
         <v>18</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F32" s="5" t="str">
-        <f t="shared" ref="F32:F33" si="6">IF(B32="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G32" s="11" t="s">
@@ -1674,24 +1679,24 @@
       </c>
       <c r="H32" s="11"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F33" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F33:F34" si="6">IF(B33="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G33" s="11" t="s">
@@ -1699,7 +1704,7 @@
       </c>
       <c r="H33" s="11"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
@@ -1710,13 +1715,13 @@
         <v>19</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F34" s="5" t="str">
-        <f t="shared" ref="F34:F35" si="7">IF(B34="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="6"/>
         <v>KVARTAL</v>
       </c>
       <c r="G34" s="11" t="s">
@@ -1724,24 +1729,24 @@
       </c>
       <c r="H34" s="11"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F35" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F35:F36" si="7">IF(B35="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G35" s="11" t="s">
@@ -1749,7 +1754,7 @@
       </c>
       <c r="H35" s="11"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -1760,13 +1765,13 @@
         <v>20</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F36" s="5" t="str">
-        <f t="shared" ref="F36:F40" si="8">IF(B36="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="7"/>
         <v>KVARTAL</v>
       </c>
       <c r="G36" s="11" t="s">
@@ -1774,24 +1779,24 @@
       </c>
       <c r="H36" s="11"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D37" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F37" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="F37:F41" si="8">IF(B37="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G37" s="11" t="s">
@@ -1799,7 +1804,7 @@
       </c>
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -1810,7 +1815,7 @@
         <v>24</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>47</v>
@@ -1824,21 +1829,21 @@
       </c>
       <c r="H38" s="11"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F39" s="5" t="str">
         <f t="shared" si="8"/>
@@ -1849,7 +1854,7 @@
       </c>
       <c r="H39" s="11"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -1860,7 +1865,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>49</v>
@@ -1874,7 +1879,7 @@
       </c>
       <c r="H40" s="11"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>6</v>
       </c>
@@ -1882,16 +1887,16 @@
         <v>58</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F41" s="5" t="str">
-        <f t="shared" ref="F41:F42" si="9">IF(B41="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="8"/>
         <v>KVARTAL</v>
       </c>
       <c r="G41" s="11" t="s">
@@ -1899,7 +1904,7 @@
       </c>
       <c r="H41" s="11"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>6</v>
       </c>
@@ -1910,13 +1915,13 @@
         <v>27</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F42" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F42:F43" si="9">IF(B42="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G42" s="11" t="s">
@@ -1924,7 +1929,7 @@
       </c>
       <c r="H42" s="11"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1932,16 +1937,16 @@
         <v>58</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F43" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>KVARTAL</v>
       </c>
       <c r="G43" s="11" t="s">
@@ -1949,7 +1954,7 @@
       </c>
       <c r="H43" s="11"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -1960,7 +1965,7 @@
         <v>31</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>48</v>
@@ -1974,7 +1979,7 @@
       </c>
       <c r="H44" s="11"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>6</v>
       </c>
@@ -1985,7 +1990,7 @@
         <v>31</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>48</v>
@@ -1999,32 +2004,32 @@
       </c>
       <c r="H45" s="11"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F46" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>ÅR</v>
+        <v>KVARTAL</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H46" s="11"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
         <v>15</v>
       </c>
@@ -2032,16 +2037,16 @@
         <v>21</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F47" s="5" t="str">
-        <f t="shared" ref="F47" si="10">IF(B47="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>ÅR</v>
       </c>
       <c r="G47" s="11" t="s">
@@ -2049,7 +2054,7 @@
       </c>
       <c r="H47" s="11"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>15</v>
       </c>
@@ -2066,7 +2071,7 @@
         <v>48</v>
       </c>
       <c r="F48" s="5" t="str">
-        <f t="shared" ref="F48" si="11">IF(B48="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F48" si="10">IF(B48="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G48" s="11" t="s">
@@ -2074,9 +2079,9 @@
       </c>
       <c r="H48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>21</v>
@@ -2085,13 +2090,13 @@
         <v>29</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F49" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F49" si="11">IF(B49="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G49" s="11" t="s">
@@ -2099,7 +2104,7 @@
       </c>
       <c r="H49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
@@ -2116,7 +2121,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="5" t="str">
-        <f t="shared" ref="F50" si="12">IF(B50="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>ÅR</v>
       </c>
       <c r="G50" s="11" t="s">
@@ -2127,7 +2132,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -2135,16 +2140,16 @@
         <v>21</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F51" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F51" si="12">IF(B51="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G51" s="11" t="s">
@@ -2152,7 +2157,7 @@
       </c>
       <c r="H51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
@@ -2163,13 +2168,13 @@
         <v>31</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F52" s="5" t="str">
-        <f t="shared" ref="F52" si="13">IF(B52="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>ÅR</v>
       </c>
       <c r="G52" s="11" t="s">
@@ -2180,24 +2185,24 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F53" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F53" si="13">IF(B53="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G53" s="11" t="s">
@@ -2205,7 +2210,7 @@
       </c>
       <c r="H53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>8</v>
       </c>
@@ -2213,16 +2218,16 @@
         <v>21</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F54" s="5" t="str">
-        <f t="shared" ref="F54" si="14">IF(B54="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>ÅR</v>
       </c>
       <c r="G54" s="11" t="s">
@@ -2233,40 +2238,40 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F55" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F55" si="14">IF(B55="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>13</v>
@@ -2275,7 +2280,7 @@
         <v>47</v>
       </c>
       <c r="F56" s="5" t="str">
-        <f t="shared" ref="F56:F58" si="15">IF(B56="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G56" s="11" t="s">
@@ -2283,15 +2288,15 @@
       </c>
       <c r="H56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>13</v>
@@ -2300,7 +2305,7 @@
         <v>47</v>
       </c>
       <c r="F57" s="5" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="F57:F59" si="15">IF(B57="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G57" s="11" t="s">
@@ -2308,15 +2313,15 @@
       </c>
       <c r="H57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>13</v>
@@ -2333,24 +2338,24 @@
       </c>
       <c r="H58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F59" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>KVARTAL</v>
       </c>
       <c r="G59" s="11" t="s">
@@ -2358,21 +2363,21 @@
       </c>
       <c r="H59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F60" s="5" t="str">
         <f t="shared" si="3"/>
@@ -2386,7 +2391,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>10</v>
       </c>
@@ -2397,13 +2402,13 @@
         <v>18</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F61" s="5" t="str">
-        <f t="shared" ref="F61:F62" si="16">IF(B61="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G61" s="11" t="s">
@@ -2414,24 +2419,24 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D62" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F62" s="5" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="F62:F63" si="16">IF(B62="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G62" s="11" t="s">
@@ -2442,7 +2447,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2453,13 +2458,13 @@
         <v>19</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F63" s="5" t="str">
-        <f t="shared" ref="F63:F67" si="17">IF(B63="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="16"/>
         <v>KVARTAL</v>
       </c>
       <c r="G63" s="11" t="s">
@@ -2470,24 +2475,24 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D64" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F64" s="5" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="F64:F68" si="17">IF(B64="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G64" s="11" t="s">
@@ -2498,7 +2503,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>10</v>
       </c>
@@ -2509,7 +2514,7 @@
         <v>20</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>47</v>
@@ -2526,18 +2531,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D66" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>47</v>
@@ -2554,7 +2559,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>10</v>
       </c>
@@ -2565,7 +2570,7 @@
         <v>24</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>47</v>
@@ -2582,24 +2587,24 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F68" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="17"/>
         <v>KVARTAL</v>
       </c>
       <c r="G68" s="11" t="s">
@@ -2610,7 +2615,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>10</v>
       </c>
@@ -2621,13 +2626,13 @@
         <v>25</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F69" s="5" t="str">
-        <f t="shared" ref="F69" si="18">IF(B69="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G69" s="11" t="s">
@@ -2638,24 +2643,24 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F70" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F70" si="18">IF(B70="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G70" s="11" t="s">
@@ -2663,7 +2668,7 @@
       </c>
       <c r="H70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
@@ -2674,13 +2679,13 @@
         <v>18</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F71" s="5" t="str">
-        <f t="shared" ref="F71:F74" si="19">IF(B71="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G71" s="11" t="s">
@@ -2688,7 +2693,7 @@
       </c>
       <c r="H71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
         <v>11</v>
       </c>
@@ -2699,13 +2704,13 @@
         <v>18</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F72" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F72:F75" si="19">IF(B72="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G72" s="11" t="s">
@@ -2713,7 +2718,7 @@
       </c>
       <c r="H72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
         <v>11</v>
       </c>
@@ -2724,7 +2729,7 @@
         <v>18</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>47</v>
@@ -2738,18 +2743,18 @@
       </c>
       <c r="H73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D74" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>47</v>
@@ -2763,7 +2768,7 @@
       </c>
       <c r="H74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
@@ -2774,13 +2779,13 @@
         <v>19</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F75" s="5" t="str">
-        <f t="shared" ref="F75:F81" si="20">IF(B75="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="19"/>
         <v>KVARTAL</v>
       </c>
       <c r="G75" s="11" t="s">
@@ -2788,7 +2793,7 @@
       </c>
       <c r="H75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
         <v>11</v>
       </c>
@@ -2799,13 +2804,13 @@
         <v>19</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F76" s="5" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="F76:F82" si="20">IF(B76="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G76" s="11" t="s">
@@ -2813,7 +2818,7 @@
       </c>
       <c r="H76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
         <v>11</v>
       </c>
@@ -2824,7 +2829,7 @@
         <v>19</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>47</v>
@@ -2838,18 +2843,18 @@
       </c>
       <c r="H77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D78" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>47</v>
@@ -2863,7 +2868,7 @@
       </c>
       <c r="H78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
         <v>11</v>
       </c>
@@ -2874,7 +2879,7 @@
         <v>20</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>47</v>
@@ -2888,18 +2893,18 @@
       </c>
       <c r="H79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D80" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>47</v>
@@ -2913,7 +2918,7 @@
       </c>
       <c r="H80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
         <v>11</v>
       </c>
@@ -2924,7 +2929,7 @@
         <v>24</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>47</v>
@@ -2938,24 +2943,24 @@
       </c>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F82" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>KVARTAL</v>
       </c>
       <c r="G82" s="11" t="s">
@@ -2963,7 +2968,7 @@
       </c>
       <c r="H82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
         <v>11</v>
       </c>
@@ -2974,13 +2979,13 @@
         <v>27</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F83" s="5" t="str">
-        <f t="shared" ref="F83:F84" si="21">IF(B83="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G83" s="11" t="s">
@@ -2988,7 +2993,7 @@
       </c>
       <c r="H83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
         <v>11</v>
       </c>
@@ -2999,13 +3004,13 @@
         <v>27</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F84" s="5" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="F84:F85" si="21">IF(B84="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G84" s="11" t="s">
@@ -3013,7 +3018,7 @@
       </c>
       <c r="H84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
         <v>11</v>
       </c>
@@ -3024,13 +3029,13 @@
         <v>27</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F85" s="5" t="str">
-        <f t="shared" ref="F85:F87" si="22">IF(B85="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="21"/>
         <v>KVARTAL</v>
       </c>
       <c r="G85" s="11" t="s">
@@ -3038,24 +3043,24 @@
       </c>
       <c r="H85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A86" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F86" s="5" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="F86:F88" si="22">IF(B86="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G86" s="11" t="s">
@@ -3063,7 +3068,7 @@
       </c>
       <c r="H86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A87" s="1" t="s">
         <v>11</v>
       </c>
@@ -3074,7 +3079,7 @@
         <v>29</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>48</v>
@@ -3088,32 +3093,32 @@
       </c>
       <c r="H87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F88" s="5" t="str">
-        <f t="shared" ref="F88" si="23">IF(B88="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" si="22"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G88" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
         <v>11</v>
       </c>
@@ -3124,13 +3129,13 @@
         <v>29</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F89" s="5" t="str">
-        <f t="shared" ref="F89:F91" si="24">IF(B89="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F89" si="23">IF(B89="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G89" s="11" t="s">
@@ -3138,7 +3143,7 @@
       </c>
       <c r="H89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
         <v>11</v>
       </c>
@@ -3149,39 +3154,39 @@
         <v>29</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F90" s="5" t="str">
+        <f t="shared" ref="F90:F92" si="24">IF(B90="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H90" s="11"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F91" s="5" t="str">
         <f t="shared" si="24"/>
         <v>ÅR</v>
-      </c>
-      <c r="G90" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H90" s="11"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A91" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F91" s="5" t="str">
-        <f t="shared" si="24"/>
-        <v>KVARTAL</v>
       </c>
       <c r="G91" s="11" t="s">
         <v>51</v>
@@ -3191,7 +3196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
         <v>12</v>
       </c>
@@ -3208,7 +3213,7 @@
         <v>47</v>
       </c>
       <c r="F92" s="5" t="str">
-        <f t="shared" ref="F92:F93" si="25">IF(B92="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="24"/>
         <v>KVARTAL</v>
       </c>
       <c r="G92" s="11" t="s">
@@ -3219,15 +3224,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>10</v>
@@ -3236,7 +3241,7 @@
         <v>47</v>
       </c>
       <c r="F93" s="5" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="F93:F94" si="25">IF(B93="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G93" s="11" t="s">
@@ -3247,7 +3252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
         <v>12</v>
       </c>
@@ -3264,7 +3269,7 @@
         <v>47</v>
       </c>
       <c r="F94" s="5" t="str">
-        <f t="shared" ref="F94:F98" si="26">IF(B94="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="25"/>
         <v>KVARTAL</v>
       </c>
       <c r="G94" s="11" t="s">
@@ -3275,15 +3280,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>10</v>
@@ -3292,7 +3297,7 @@
         <v>47</v>
       </c>
       <c r="F95" s="5" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="F95:F99" si="26">IF(B95="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G95" s="11" t="s">
@@ -3303,7 +3308,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
         <v>12</v>
       </c>
@@ -3331,15 +3336,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>10</v>
@@ -3359,7 +3364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A98" s="1" t="s">
         <v>12</v>
       </c>
@@ -3387,24 +3392,24 @@
         <v>60</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A99" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F99" s="5" t="str">
-        <f t="shared" ref="F99:F106" si="27">IF(B99="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="26"/>
         <v>KVARTAL</v>
       </c>
       <c r="G99" s="11" t="s">
@@ -3415,7 +3420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
         <v>12</v>
       </c>
@@ -3432,7 +3437,7 @@
         <v>48</v>
       </c>
       <c r="F100" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="F100:F107" si="27">IF(B100="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G100" s="11" t="s">
@@ -3443,25 +3448,25 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F101" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>ÅR</v>
+        <v>KVARTAL</v>
       </c>
       <c r="G101" s="11" t="s">
         <v>51</v>
@@ -3471,21 +3476,21 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F102" s="5" t="str">
         <f t="shared" si="27"/>
@@ -3496,7 +3501,7 @@
       </c>
       <c r="H102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
         <v>16</v>
       </c>
@@ -3507,13 +3512,13 @@
         <v>25</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F103" s="5" t="str">
-        <f t="shared" ref="F103:F104" si="28">IF(B103="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="27"/>
         <v>ÅR</v>
       </c>
       <c r="G103" s="11" t="s">
@@ -3521,7 +3526,7 @@
       </c>
       <c r="H103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
         <v>16</v>
       </c>
@@ -3532,71 +3537,71 @@
         <v>25</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F104" s="5" t="str">
+        <f t="shared" ref="F104:F105" si="28">IF(B104="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
+      </c>
+      <c r="G104" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H104" s="11"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A105" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F104" s="5" t="str">
+      <c r="F105" s="5" t="str">
         <f t="shared" si="28"/>
         <v>ÅR</v>
       </c>
-      <c r="G104" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H104" s="11"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A105" s="1" t="s">
+      <c r="G105" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H105" s="11"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A106" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F105" s="5" t="str">
-        <f t="shared" ref="F105" si="29">IF(B105="2024","ÅR","KVARTAL")</f>
+      <c r="F106" s="5" t="str">
+        <f t="shared" ref="F106" si="29">IF(B106="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
-      <c r="G105" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H105" s="11"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A106" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F106" s="5" t="str">
-        <f t="shared" si="27"/>
-        <v>KVARTAL</v>
-      </c>
       <c r="G106" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
         <v>13</v>
       </c>
@@ -3607,13 +3612,13 @@
         <v>18</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F107" s="5" t="str">
-        <f t="shared" ref="F107:F110" si="30">IF(B107="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="27"/>
         <v>KVARTAL</v>
       </c>
       <c r="G107" s="11" t="s">
@@ -3621,7 +3626,7 @@
       </c>
       <c r="H107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
         <v>13</v>
       </c>
@@ -3632,13 +3637,13 @@
         <v>18</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F108" s="5" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="F108:F111" si="30">IF(B108="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G108" s="11" t="s">
@@ -3646,9 +3651,9 @@
       </c>
       <c r="H108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A109" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>17</v>
@@ -3657,38 +3662,38 @@
         <v>18</v>
       </c>
       <c r="D109" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F109" s="5" t="str">
+        <f t="shared" si="30"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G109" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H109" s="11"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A110" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F109" s="5" t="str">
-        <f t="shared" ref="F109" si="31">IF(B109="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G109" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H109" s="11"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A110" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E110" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F110" s="5" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="F110" si="31">IF(B110="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G110" s="11" t="s">
@@ -3696,7 +3701,7 @@
       </c>
       <c r="H110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A111" s="1" t="s">
         <v>13</v>
       </c>
@@ -3707,13 +3712,13 @@
         <v>19</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F111" s="5" t="str">
-        <f t="shared" ref="F111:F128" si="32">IF(B111="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="30"/>
         <v>KVARTAL</v>
       </c>
       <c r="G111" s="11" t="s">
@@ -3721,7 +3726,7 @@
       </c>
       <c r="H111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A112" s="1" t="s">
         <v>13</v>
       </c>
@@ -3732,13 +3737,13 @@
         <v>19</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F112" s="5" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="F112:F130" si="32">IF(B112="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G112" s="11" t="s">
@@ -3746,9 +3751,9 @@
       </c>
       <c r="H112" s="11"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A113" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>18</v>
@@ -3757,38 +3762,38 @@
         <v>19</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F113" s="5" t="str">
+        <f t="shared" si="32"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G113" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H113" s="11"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A114" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F113" s="5" t="str">
-        <f t="shared" ref="F113" si="33">IF(B113="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G113" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H113" s="11"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A114" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E114" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F114" s="5" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="F114" si="33">IF(B114="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G114" s="11" t="s">
@@ -3796,7 +3801,7 @@
       </c>
       <c r="H114" s="11"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A115" s="1" t="s">
         <v>13</v>
       </c>
@@ -3807,7 +3812,7 @@
         <v>20</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>47</v>
@@ -3821,7 +3826,7 @@
       </c>
       <c r="H115" s="11"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A116" s="1" t="s">
         <v>13</v>
       </c>
@@ -3832,13 +3837,13 @@
         <v>20</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F116" s="5" t="str">
-        <f t="shared" ref="F116:F117" si="34">IF(B116="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="32"/>
         <v>KVARTAL</v>
       </c>
       <c r="G116" s="11" t="s">
@@ -3846,9 +3851,9 @@
       </c>
       <c r="H116" s="11"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A117" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>19</v>
@@ -3857,46 +3862,46 @@
         <v>20</v>
       </c>
       <c r="D117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F117" s="5" t="str">
+        <f t="shared" ref="F117:F118" si="34">IF(B117="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G117" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H117" s="11"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A118" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F117" s="5" t="str">
+      <c r="E118" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F118" s="5" t="str">
         <f t="shared" si="34"/>
         <v>KVARTAL</v>
       </c>
-      <c r="G117" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H117" s="11"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A118" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F118" s="5" t="str">
-        <f t="shared" si="32"/>
-        <v>KVARTAL</v>
-      </c>
       <c r="G118" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H118" s="11"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A119" s="1" t="s">
         <v>13</v>
       </c>
@@ -3907,7 +3912,7 @@
         <v>24</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>47</v>
@@ -3921,7 +3926,7 @@
       </c>
       <c r="H119" s="11"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A120" s="1" t="s">
         <v>13</v>
       </c>
@@ -3932,13 +3937,13 @@
         <v>24</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F120" s="5" t="str">
-        <f t="shared" ref="F120:F121" si="35">IF(B120="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="32"/>
         <v>KVARTAL</v>
       </c>
       <c r="G120" s="11" t="s">
@@ -3946,9 +3951,9 @@
       </c>
       <c r="H120" s="11"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A121" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>20</v>
@@ -3957,13 +3962,13 @@
         <v>24</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F121" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="F121:F122" si="35">IF(B121="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G121" s="11" t="s">
@@ -3971,57 +3976,57 @@
       </c>
       <c r="H121" s="11"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A122" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F122" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G122" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H122" s="11"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F122" s="5" t="str">
+      <c r="E123" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F123" s="5" t="str">
         <f t="shared" si="32"/>
         <v>ÅR</v>
       </c>
-      <c r="G122" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H122" s="11"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A123" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F123" s="5" t="str">
-        <f t="shared" ref="F123:F125" si="36">IF(B123="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
-      </c>
       <c r="G123" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H123" s="11"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A124" s="1" t="s">
         <v>13</v>
       </c>
@@ -4032,13 +4037,13 @@
         <v>24</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F124" s="5" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="F124:F126" si="36">IF(B124="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G124" s="11" t="s">
@@ -4046,7 +4051,7 @@
       </c>
       <c r="H124" s="11"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A125" s="1" t="s">
         <v>13</v>
       </c>
@@ -4054,10 +4059,10 @@
         <v>21</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>47</v>
@@ -4071,7 +4076,7 @@
       </c>
       <c r="H125" s="11"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A126" s="1" t="s">
         <v>13</v>
       </c>
@@ -4079,16 +4084,16 @@
         <v>21</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F126" s="5" t="str">
-        <f t="shared" ref="F126" si="37">IF(B126="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="36"/>
         <v>ÅR</v>
       </c>
       <c r="G126" s="11" t="s">
@@ -4096,32 +4101,32 @@
       </c>
       <c r="H126" s="11"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A127" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F127" s="5" t="str">
-        <f t="shared" si="32"/>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F127" si="37">IF(B127="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G127" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H127" s="11"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A128" s="1" t="s">
         <v>13</v>
       </c>
@@ -4132,132 +4137,132 @@
         <v>29</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F128" s="5" t="str">
+        <f t="shared" ref="F128" si="38">IF(B128="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
+      </c>
+      <c r="G128" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H128" s="11"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F129" s="5" t="str">
+        <f t="shared" si="32"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G129" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H129" s="11"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A130" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F130" s="5" t="str">
         <f t="shared" si="32"/>
         <v>ÅR</v>
       </c>
-      <c r="G128" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H128" s="11"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A129" s="1" t="s">
+      <c r="G130" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H130" s="11"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A131" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C131" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E131" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F129" s="5" t="str">
-        <f t="shared" ref="F129:F131" si="38">IF(B129="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G129" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H129" s="11"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A130" s="1" t="s">
+      <c r="F131" s="5" t="str">
+        <f t="shared" ref="F131:F133" si="39">IF(B131="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G131" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H131" s="11"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A132" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C132" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F130" s="5" t="str">
-        <f t="shared" si="38"/>
+      <c r="F132" s="5" t="str">
+        <f t="shared" si="39"/>
         <v>ÅR</v>
       </c>
-      <c r="G130" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H130" s="11"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A131" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F131" s="5" t="str">
-        <f t="shared" si="38"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G131" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H131" s="11"/>
-      <c r="I131" s="1" t="s">
+      <c r="G132" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H132" s="11"/>
+      <c r="I132" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A132" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F132" s="5" t="str">
-        <f t="shared" ref="F132" si="39">IF(B132="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G132" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H132" s="11"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A133" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>10</v>
@@ -4266,26 +4271,23 @@
         <v>47</v>
       </c>
       <c r="F133" s="5" t="str">
-        <f t="shared" ref="F133:F137" si="40">IF(B133="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="39"/>
         <v>KVARTAL</v>
       </c>
       <c r="G133" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H133" s="11"/>
-      <c r="I133" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.6">
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A134" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>11</v>
@@ -4294,23 +4296,26 @@
         <v>47</v>
       </c>
       <c r="F134" s="5" t="str">
-        <f t="shared" ref="F134" si="41">IF(B134="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F134" si="40">IF(B134="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G134" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H134" s="11"/>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="I134" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A135" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>10</v>
@@ -4319,26 +4324,23 @@
         <v>47</v>
       </c>
       <c r="F135" s="5" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="F135:F139" si="41">IF(B135="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G135" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H135" s="11"/>
-      <c r="I135" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.6">
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A136" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>11</v>
@@ -4354,16 +4356,19 @@
         <v>51</v>
       </c>
       <c r="H136" s="11"/>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="I136" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A137" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>10</v>
@@ -4372,26 +4377,23 @@
         <v>47</v>
       </c>
       <c r="F137" s="5" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>KVARTAL</v>
       </c>
       <c r="G137" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H137" s="11"/>
-      <c r="I137" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.6">
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A138" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>11</v>
@@ -4407,486 +4409,539 @@
         <v>51</v>
       </c>
       <c r="H138" s="11"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="I138" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A139" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E139" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F139" s="5" t="str">
+        <f t="shared" si="41"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G139" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H139" s="11"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A140" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F140" s="5" t="str">
+        <f t="shared" ref="F140" si="44">IF(B140="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G140" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H140" s="11"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A141" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F139" s="5" t="str">
-        <f t="shared" ref="F139:F192" si="44">IF(B139="2024","ÅR","KVARTAL")</f>
+      <c r="F141" s="5" t="str">
+        <f t="shared" ref="F141:F194" si="45">IF(B141="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
-      <c r="G139" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H139" s="11"/>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="F140" s="5" t="str">
-        <f t="shared" si="44"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G140" s="11"/>
-      <c r="H140" s="11"/>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="F141" s="5" t="str">
-        <f t="shared" si="44"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G141" s="11"/>
+      <c r="G141" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="H141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.4">
       <c r="F142" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G142" s="11"/>
       <c r="H142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.4">
       <c r="F143" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G143" s="11"/>
       <c r="H143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.4">
       <c r="F144" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G144" s="11"/>
       <c r="H144" s="11"/>
     </row>
-    <row r="145" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="145" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F145" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G145" s="11"/>
       <c r="H145" s="11"/>
     </row>
-    <row r="146" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="146" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F146" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G146" s="11"/>
       <c r="H146" s="11"/>
     </row>
-    <row r="147" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="147" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F147" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G147" s="11"/>
       <c r="H147" s="11"/>
     </row>
-    <row r="148" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="148" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F148" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G148" s="11"/>
       <c r="H148" s="11"/>
     </row>
-    <row r="149" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="149" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F149" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G149" s="11"/>
       <c r="H149" s="11"/>
     </row>
-    <row r="150" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="150" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F150" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G150" s="11"/>
       <c r="H150" s="11"/>
     </row>
-    <row r="151" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="151" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F151" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G151" s="11"/>
       <c r="H151" s="11"/>
     </row>
-    <row r="152" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="152" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F152" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G152" s="11"/>
       <c r="H152" s="11"/>
     </row>
-    <row r="153" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="153" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F153" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G153" s="11"/>
       <c r="H153" s="11"/>
     </row>
-    <row r="154" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="154" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F154" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G154" s="11"/>
       <c r="H154" s="11"/>
     </row>
-    <row r="155" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="155" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F155" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G155" s="11"/>
       <c r="H155" s="11"/>
     </row>
-    <row r="156" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="156" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F156" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G156" s="11"/>
       <c r="H156" s="11"/>
     </row>
-    <row r="157" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="157" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F157" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G157" s="11"/>
       <c r="H157" s="11"/>
     </row>
-    <row r="158" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="158" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F158" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G158" s="11"/>
       <c r="H158" s="11"/>
     </row>
-    <row r="159" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="159" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F159" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G159" s="11"/>
       <c r="H159" s="11"/>
     </row>
-    <row r="160" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="160" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F160" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G160" s="11"/>
       <c r="H160" s="11"/>
     </row>
-    <row r="161" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="161" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F161" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G161" s="11"/>
       <c r="H161" s="11"/>
     </row>
-    <row r="162" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="162" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F162" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G162" s="11"/>
       <c r="H162" s="11"/>
     </row>
-    <row r="163" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="163" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F163" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G163" s="11"/>
       <c r="H163" s="11"/>
     </row>
-    <row r="164" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="164" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F164" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G164" s="11"/>
       <c r="H164" s="11"/>
     </row>
-    <row r="165" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="165" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F165" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G165" s="11"/>
       <c r="H165" s="11"/>
     </row>
-    <row r="166" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="166" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F166" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G166" s="11"/>
       <c r="H166" s="11"/>
     </row>
-    <row r="167" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="167" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F167" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G167" s="11"/>
       <c r="H167" s="11"/>
     </row>
-    <row r="168" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="168" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F168" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G168" s="11"/>
       <c r="H168" s="11"/>
     </row>
-    <row r="169" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="169" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F169" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G169" s="11"/>
       <c r="H169" s="11"/>
     </row>
-    <row r="170" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="170" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F170" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G170" s="11"/>
       <c r="H170" s="11"/>
     </row>
-    <row r="171" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="171" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F171" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G171" s="11"/>
       <c r="H171" s="11"/>
     </row>
-    <row r="172" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="172" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F172" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G172" s="11"/>
       <c r="H172" s="11"/>
     </row>
-    <row r="173" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="173" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F173" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G173" s="11"/>
       <c r="H173" s="11"/>
     </row>
-    <row r="174" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="174" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F174" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G174" s="11"/>
       <c r="H174" s="11"/>
     </row>
-    <row r="175" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="175" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F175" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G175" s="11"/>
       <c r="H175" s="11"/>
     </row>
-    <row r="176" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="176" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F176" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G176" s="11"/>
       <c r="H176" s="11"/>
     </row>
-    <row r="177" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="177" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F177" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G177" s="11"/>
       <c r="H177" s="11"/>
     </row>
-    <row r="178" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="178" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F178" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G178" s="11"/>
       <c r="H178" s="11"/>
     </row>
-    <row r="179" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="179" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F179" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G179" s="11"/>
       <c r="H179" s="11"/>
     </row>
-    <row r="180" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="180" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F180" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G180" s="11"/>
       <c r="H180" s="11"/>
     </row>
-    <row r="181" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="181" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F181" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G181" s="11"/>
       <c r="H181" s="11"/>
     </row>
-    <row r="182" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="182" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F182" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G182" s="11"/>
       <c r="H182" s="11"/>
     </row>
-    <row r="183" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="183" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F183" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G183" s="11"/>
       <c r="H183" s="11"/>
     </row>
-    <row r="184" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="184" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F184" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G184" s="11"/>
       <c r="H184" s="11"/>
     </row>
-    <row r="185" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="185" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F185" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G185" s="11"/>
       <c r="H185" s="11"/>
     </row>
-    <row r="186" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="186" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F186" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G186" s="11"/>
       <c r="H186" s="11"/>
     </row>
-    <row r="187" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="187" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F187" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G187" s="11"/>
       <c r="H187" s="11"/>
     </row>
-    <row r="188" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="188" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F188" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G188" s="11"/>
       <c r="H188" s="11"/>
     </row>
-    <row r="189" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="189" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F189" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G189" s="11"/>
       <c r="H189" s="11"/>
     </row>
-    <row r="190" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="190" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F190" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G190" s="11"/>
       <c r="H190" s="11"/>
     </row>
-    <row r="191" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="191" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F191" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G191" s="11"/>
       <c r="H191" s="11"/>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.6">
+    <row r="192" spans="6:8" x14ac:dyDescent="0.4">
       <c r="F192" s="5" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>KVARTAL</v>
       </c>
       <c r="G192" s="11"/>
       <c r="H192" s="11"/>
     </row>
+    <row r="193" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F193" s="5" t="str">
+        <f t="shared" si="45"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G193" s="11"/>
+      <c r="H193" s="11"/>
+    </row>
+    <row r="194" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F194" s="5" t="str">
+        <f t="shared" si="45"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G194" s="11"/>
+      <c r="H194" s="11"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I192" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}"/>
+  <autoFilter ref="A1:I193" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8A352F04-E99B-434A-B2F4-238791E4E11C}">
-          <x14:formula1>
-            <xm:f>LISTER!$B$2:$B$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B192</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4699882C-A539-431A-9F19-F1B3185EADBF}">
           <x14:formula1>
             <xm:f>LISTER!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D192 A2:A192</xm:sqref>
+          <xm:sqref>D2:D194 A2:A194</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{424D03F4-B91D-4C98-9865-9386CE07D412}">
           <x14:formula1>
             <xm:f>LISTER!$C$2:$C$13</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C192</xm:sqref>
+          <xm:sqref>C2:C194</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C0FD7FC9-0A01-4E4D-963C-4616ACB0FCFE}">
           <x14:formula1>
             <xm:f>LISTER!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E192</xm:sqref>
+          <xm:sqref>E2:E194</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8A352F04-E99B-434A-B2F4-238791E4E11C}">
+          <x14:formula1>
+            <xm:f>LISTER!$B$2:$B$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B194</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4897,15 +4952,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4AC0EB3-E901-4261-932E-F1531117BF74}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="19.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.453125" style="1"/>
+    <col min="4" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
@@ -4919,7 +4974,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>5</v>
       </c>
@@ -4933,7 +4988,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
@@ -4947,7 +5002,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4961,7 +5016,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -4972,7 +5027,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4983,37 +5038,40 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="C9" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5021,7 +5079,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
@@ -5029,7 +5087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5037,7 +5095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
         <v>16</v>
       </c>

--- a/nr/NR_sammenhenger.xlsx
+++ b/nr/NR_sammenhenger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ssbno-my.sharepoint.com/personal/thb_ssb_no/Documents/Infografikk arbeidsmappe/_Seksjon 702/NR/Nr ws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="1_{C5C1F706-3044-4F05-A798-4088D00B8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4087D345-1D7E-4FFC-B341-4E0D840E8049}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="1_{C5C1F706-3044-4F05-A798-4088D00B8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29E0316E-BEA5-4AF0-84FE-D4C23C894AC1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9063F859-FFB0-4ECD-8E4A-53A11DB5693E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="LISTER" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SAMMENHENGER!$A$1:$I$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SAMMENHENGER!$A$1:$I$190</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="64">
   <si>
     <t>LEVERANDØR</t>
   </si>
@@ -355,6 +355,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -819,7 +823,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}">
-  <dimension ref="A1:I194"/>
+  <dimension ref="A1:I191"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1173,20 +1177,20 @@
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F14" s="5" t="str">
-        <f>IF(B14="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F14" si="1">IF(B14="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>51</v>
@@ -1203,16 +1207,16 @@
         <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="5" t="str">
-        <f t="shared" ref="F15:F17" si="1">IF(B15="2024","ÅR","KVARTAL")</f>
+        <f>IF(B15="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G15" s="11" t="s">
@@ -1230,16 +1234,16 @@
         <v>58</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F16" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F16:F18" si="2">IF(B16="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G16" s="11" t="s">
@@ -1254,20 +1258,20 @@
         <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F17" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>ÅR</v>
+        <f t="shared" si="2"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>51</v>
@@ -1281,20 +1285,20 @@
         <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F18" s="5" t="str">
-        <f>IF(B18="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
+        <f t="shared" si="2"/>
+        <v>ÅR</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>51</v>
@@ -1311,16 +1315,16 @@
         <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F19" s="5" t="str">
-        <f t="shared" ref="F19:F21" si="2">IF(B19="2024","ÅR","KVARTAL")</f>
+        <f>IF(B19="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G19" s="11" t="s">
@@ -1338,16 +1342,16 @@
         <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F20" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="F20:F80" si="3">IF(B20="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G20" s="11" t="s">
@@ -1362,20 +1366,20 @@
         <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F21" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>ÅR</v>
+        <f t="shared" si="3"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>51</v>
@@ -1389,20 +1393,20 @@
         <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F22" s="5" t="str">
-        <f>IF(B22="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
+        <f t="shared" si="3"/>
+        <v>ÅR</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>51</v>
@@ -1416,20 +1420,20 @@
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F23" s="5" t="str">
-        <f t="shared" ref="F23:F83" si="3">IF(B23="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
+        <f t="shared" si="3"/>
+        <v>ÅR</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>51</v>
@@ -1443,20 +1447,20 @@
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F24:F25" si="4">IF(B24="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>51</v>
@@ -1470,20 +1474,20 @@
         <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F25" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>ÅR</v>
+        <f t="shared" si="4"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>51</v>
@@ -1503,13 +1507,13 @@
         <v>29</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F26" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F26" si="5">IF(B26="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G26" s="11" t="s">
@@ -1524,20 +1528,20 @@
         <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F27" s="5" t="str">
-        <f t="shared" ref="F27:F28" si="4">IF(B27="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f>IF(B27="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>51</v>
@@ -1554,16 +1558,16 @@
         <v>58</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F28" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(B28="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G28" s="11" t="s">
@@ -1575,103 +1579,97 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F29" s="5" t="str">
-        <f t="shared" ref="F29" si="5">IF(B29="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" si="3"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="H29" s="11"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F30" s="5" t="str">
-        <f>IF(B30="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F30:F31" si="6">IF(B30="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="H30" s="11"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F31" s="5" t="str">
-        <f>IF(B31="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="6"/>
         <v>KVARTAL</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="H31" s="11"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F32" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F32:F33" si="7">IF(B32="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G32" s="11" t="s">
@@ -1679,24 +1677,24 @@
       </c>
       <c r="H32" s="11"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F33" s="5" t="str">
-        <f t="shared" ref="F33:F34" si="6">IF(B33="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="7"/>
         <v>KVARTAL</v>
       </c>
       <c r="G33" s="11" t="s">
@@ -1704,24 +1702,24 @@
       </c>
       <c r="H33" s="11"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F34" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F34:F38" si="8">IF(B34="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G34" s="11" t="s">
@@ -1729,24 +1727,24 @@
       </c>
       <c r="H34" s="11"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F35" s="5" t="str">
-        <f t="shared" ref="F35:F36" si="7">IF(B35="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="8"/>
         <v>KVARTAL</v>
       </c>
       <c r="G35" s="11" t="s">
@@ -1754,24 +1752,24 @@
       </c>
       <c r="H35" s="11"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F36" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>KVARTAL</v>
       </c>
       <c r="G36" s="11" t="s">
@@ -1779,24 +1777,24 @@
       </c>
       <c r="H36" s="11"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F37" s="5" t="str">
-        <f t="shared" ref="F37:F41" si="8">IF(B37="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="8"/>
         <v>KVARTAL</v>
       </c>
       <c r="G37" s="11" t="s">
@@ -1804,21 +1802,21 @@
       </c>
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F38" s="5" t="str">
         <f t="shared" si="8"/>
@@ -1829,24 +1827,24 @@
       </c>
       <c r="H38" s="11"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F39" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="F39:F40" si="9">IF(B39="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G39" s="11" t="s">
@@ -1854,7 +1852,7 @@
       </c>
       <c r="H39" s="11"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -1862,16 +1860,16 @@
         <v>58</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F40" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>KVARTAL</v>
       </c>
       <c r="G40" s="11" t="s">
@@ -1879,7 +1877,7 @@
       </c>
       <c r="H40" s="11"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>6</v>
       </c>
@@ -1887,16 +1885,16 @@
         <v>58</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F41" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G41" s="11" t="s">
@@ -1904,7 +1902,7 @@
       </c>
       <c r="H41" s="11"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>6</v>
       </c>
@@ -1912,16 +1910,16 @@
         <v>58</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F42" s="5" t="str">
-        <f t="shared" ref="F42:F43" si="9">IF(B42="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G42" s="11" t="s">
@@ -1929,7 +1927,7 @@
       </c>
       <c r="H42" s="11"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1937,16 +1935,16 @@
         <v>58</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F43" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G43" s="11" t="s">
@@ -1954,65 +1952,65 @@
       </c>
       <c r="H43" s="11"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F44" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>KVARTAL</v>
+        <v>ÅR</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H44" s="11"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F45" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F45" si="10">IF(B45="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H45" s="11"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>13</v>
@@ -2021,29 +2019,29 @@
         <v>48</v>
       </c>
       <c r="F46" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F46" si="11">IF(B46="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H46" s="11"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F47" s="5" t="str">
         <f t="shared" si="3"/>
@@ -2053,10 +2051,13 @@
         <v>51</v>
       </c>
       <c r="H47" s="11"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I47" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>21</v>
@@ -2065,13 +2066,13 @@
         <v>29</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F48" s="5" t="str">
-        <f t="shared" ref="F48" si="10">IF(B48="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F48" si="12">IF(B48="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G48" s="11" t="s">
@@ -2081,28 +2082,31 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F49" s="5" t="str">
-        <f t="shared" ref="F49" si="11">IF(B49="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>ÅR</v>
       </c>
       <c r="G49" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H49" s="11"/>
+      <c r="I49" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
@@ -2112,54 +2116,54 @@
         <v>21</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F50" s="5" t="str">
+        <f t="shared" ref="F50" si="13">IF(B50="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H50" s="11"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" s="5" t="str">
         <f t="shared" si="3"/>
         <v>ÅR</v>
       </c>
-      <c r="G50" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H50" s="11"/>
-      <c r="I50" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F51" s="5" t="str">
-        <f t="shared" ref="F51" si="12">IF(B51="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
-      </c>
       <c r="G51" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H51" s="11"/>
+      <c r="I51" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>21</v>
@@ -2168,42 +2172,39 @@
         <v>31</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F52" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F52" si="14">IF(B52="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H52" s="11"/>
-      <c r="I52" s="1" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F53" s="5" t="str">
-        <f t="shared" ref="F53" si="13">IF(B53="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" si="3"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G53" s="11" t="s">
         <v>51</v>
@@ -2212,51 +2213,48 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F54" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>ÅR</v>
+        <f t="shared" ref="F54:F56" si="15">IF(B54="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H54" s="11"/>
-      <c r="I54" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F55" s="5" t="str">
-        <f t="shared" ref="F55" si="14">IF(B55="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" si="15"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>51</v>
@@ -2268,10 +2266,10 @@
         <v>9</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>13</v>
@@ -2280,7 +2278,7 @@
         <v>47</v>
       </c>
       <c r="F56" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>KVARTAL</v>
       </c>
       <c r="G56" s="11" t="s">
@@ -2293,94 +2291,103 @@
         <v>9</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F57" s="5" t="str">
-        <f t="shared" ref="F57:F59" si="15">IF(B57="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H57" s="11"/>
+      <c r="I57" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F58" s="5" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H58" s="11"/>
+      <c r="I58" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F59" s="5" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="F59:F60" si="16">IF(B59="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H59" s="11"/>
+      <c r="I59" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F60" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="16"/>
         <v>KVARTAL</v>
       </c>
       <c r="G60" s="11" t="s">
@@ -2396,19 +2403,19 @@
         <v>10</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F61" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F61:F65" si="17">IF(B61="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G61" s="11" t="s">
@@ -2424,19 +2431,19 @@
         <v>10</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F62" s="5" t="str">
-        <f t="shared" ref="F62:F63" si="16">IF(B62="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="17"/>
         <v>KVARTAL</v>
       </c>
       <c r="G62" s="11" t="s">
@@ -2452,19 +2459,19 @@
         <v>10</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F63" s="5" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>KVARTAL</v>
       </c>
       <c r="G63" s="11" t="s">
@@ -2480,19 +2487,19 @@
         <v>10</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F64" s="5" t="str">
-        <f t="shared" ref="F64:F68" si="17">IF(B64="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="17"/>
         <v>KVARTAL</v>
       </c>
       <c r="G64" s="11" t="s">
@@ -2508,13 +2515,13 @@
         <v>10</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>47</v>
@@ -2536,19 +2543,19 @@
         <v>10</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F66" s="5" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G66" s="11" t="s">
@@ -2564,103 +2571,94 @@
         <v>10</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F67" s="5" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="F67" si="18">IF(B67="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G67" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H67" s="11"/>
-      <c r="I67" s="1" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F68" s="5" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H68" s="11"/>
-      <c r="I68" s="1" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F69" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F69:F72" si="19">IF(B69="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H69" s="11"/>
-      <c r="I69" s="1" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F70" s="5" t="str">
-        <f t="shared" ref="F70" si="18">IF(B70="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="19"/>
         <v>KVARTAL</v>
       </c>
       <c r="G70" s="11" t="s">
@@ -2679,13 +2677,13 @@
         <v>18</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F71" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="19"/>
         <v>KVARTAL</v>
       </c>
       <c r="G71" s="11" t="s">
@@ -2698,19 +2696,19 @@
         <v>11</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F72" s="5" t="str">
-        <f t="shared" ref="F72:F75" si="19">IF(B72="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="19"/>
         <v>KVARTAL</v>
       </c>
       <c r="G72" s="11" t="s">
@@ -2723,19 +2721,19 @@
         <v>11</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F73" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F73:F79" si="20">IF(B73="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G73" s="11" t="s">
@@ -2748,19 +2746,19 @@
         <v>11</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F74" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>KVARTAL</v>
       </c>
       <c r="G74" s="11" t="s">
@@ -2779,13 +2777,13 @@
         <v>19</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F75" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>KVARTAL</v>
       </c>
       <c r="G75" s="11" t="s">
@@ -2798,19 +2796,19 @@
         <v>11</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F76" s="5" t="str">
-        <f t="shared" ref="F76:F82" si="20">IF(B76="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="20"/>
         <v>KVARTAL</v>
       </c>
       <c r="G76" s="11" t="s">
@@ -2823,13 +2821,13 @@
         <v>11</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>47</v>
@@ -2848,13 +2846,13 @@
         <v>11</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>47</v>
@@ -2873,13 +2871,13 @@
         <v>11</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>47</v>
@@ -2898,19 +2896,19 @@
         <v>11</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F80" s="5" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>KVARTAL</v>
       </c>
       <c r="G80" s="11" t="s">
@@ -2923,19 +2921,19 @@
         <v>11</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F81" s="5" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="F81:F82" si="21">IF(B81="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G81" s="11" t="s">
@@ -2948,19 +2946,19 @@
         <v>11</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F82" s="5" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>KVARTAL</v>
       </c>
       <c r="G82" s="11" t="s">
@@ -2979,13 +2977,13 @@
         <v>27</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F83" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F83:F85" si="22">IF(B83="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G83" s="11" t="s">
@@ -2998,19 +2996,19 @@
         <v>11</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F84" s="5" t="str">
-        <f t="shared" ref="F84:F85" si="21">IF(B84="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="22"/>
         <v>KVARTAL</v>
       </c>
       <c r="G84" s="11" t="s">
@@ -3023,19 +3021,19 @@
         <v>11</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F85" s="5" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>KVARTAL</v>
       </c>
       <c r="G85" s="11" t="s">
@@ -3048,20 +3046,20 @@
         <v>11</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F86" s="5" t="str">
-        <f t="shared" ref="F86:F88" si="22">IF(B86="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F86" si="23">IF(B86="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G86" s="11" t="s">
         <v>51</v>
@@ -3073,20 +3071,20 @@
         <v>11</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F87" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F87:F89" si="24">IF(B87="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G87" s="11" t="s">
         <v>51</v>
@@ -3098,102 +3096,111 @@
         <v>11</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F88" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>KVARTAL</v>
+        <f t="shared" si="24"/>
+        <v>ÅR</v>
       </c>
       <c r="G88" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H88" s="11"/>
+      <c r="I88" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F89" s="5" t="str">
-        <f t="shared" ref="F89" si="23">IF(B89="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" si="24"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G89" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H89" s="11"/>
+      <c r="I89" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F90" s="5" t="str">
-        <f t="shared" ref="F90:F92" si="24">IF(B90="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" ref="F90:F91" si="25">IF(B90="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
       </c>
       <c r="G90" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H90" s="11"/>
+      <c r="I90" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F91" s="5" t="str">
-        <f t="shared" si="24"/>
-        <v>ÅR</v>
+        <f t="shared" si="25"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G91" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H91" s="11"/>
       <c r="I91" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.4">
@@ -3201,10 +3208,10 @@
         <v>12</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>10</v>
@@ -3213,7 +3220,7 @@
         <v>47</v>
       </c>
       <c r="F92" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="F92:F96" si="26">IF(B92="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G92" s="11" t="s">
@@ -3221,7 +3228,7 @@
       </c>
       <c r="H92" s="11"/>
       <c r="I92" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.4">
@@ -3229,10 +3236,10 @@
         <v>12</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>10</v>
@@ -3241,7 +3248,7 @@
         <v>47</v>
       </c>
       <c r="F93" s="5" t="str">
-        <f t="shared" ref="F93:F94" si="25">IF(B93="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="26"/>
         <v>KVARTAL</v>
       </c>
       <c r="G93" s="11" t="s">
@@ -3249,7 +3256,7 @@
       </c>
       <c r="H93" s="11"/>
       <c r="I93" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.4">
@@ -3257,10 +3264,10 @@
         <v>12</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>10</v>
@@ -3269,7 +3276,7 @@
         <v>47</v>
       </c>
       <c r="F94" s="5" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>KVARTAL</v>
       </c>
       <c r="G94" s="11" t="s">
@@ -3277,7 +3284,7 @@
       </c>
       <c r="H94" s="11"/>
       <c r="I94" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.4">
@@ -3285,10 +3292,10 @@
         <v>12</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>10</v>
@@ -3297,7 +3304,7 @@
         <v>47</v>
       </c>
       <c r="F95" s="5" t="str">
-        <f t="shared" ref="F95:F99" si="26">IF(B95="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="26"/>
         <v>KVARTAL</v>
       </c>
       <c r="G95" s="11" t="s">
@@ -3305,7 +3312,7 @@
       </c>
       <c r="H95" s="11"/>
       <c r="I95" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.4">
@@ -3313,10 +3320,10 @@
         <v>12</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>10</v>
@@ -3333,7 +3340,7 @@
       </c>
       <c r="H96" s="11"/>
       <c r="I96" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.4">
@@ -3341,19 +3348,19 @@
         <v>12</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F97" s="5" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="F97:F104" si="27">IF(B97="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G97" s="11" t="s">
@@ -3361,7 +3368,7 @@
       </c>
       <c r="H97" s="11"/>
       <c r="I97" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.4">
@@ -3369,19 +3376,19 @@
         <v>12</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F98" s="5" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>KVARTAL</v>
       </c>
       <c r="G98" s="11" t="s">
@@ -3389,7 +3396,7 @@
       </c>
       <c r="H98" s="11"/>
       <c r="I98" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.4">
@@ -3397,103 +3404,94 @@
         <v>12</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F99" s="5" t="str">
-        <f t="shared" si="26"/>
-        <v>KVARTAL</v>
+        <f t="shared" si="27"/>
+        <v>ÅR</v>
       </c>
       <c r="G99" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H99" s="11"/>
-      <c r="I99" s="1" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F100" s="5" t="str">
-        <f t="shared" ref="F100:F107" si="27">IF(B100="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
+        <f t="shared" si="27"/>
+        <v>ÅR</v>
       </c>
       <c r="G100" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H100" s="11"/>
-      <c r="I100" s="1" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F101" s="5" t="str">
-        <f t="shared" si="27"/>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F101:F102" si="28">IF(B101="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G101" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H101" s="11"/>
-      <c r="I101" s="1" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F102" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>ÅR</v>
       </c>
       <c r="G102" s="11" t="s">
@@ -3512,13 +3510,13 @@
         <v>25</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F103" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="F103" si="29">IF(B103="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G103" s="11" t="s">
@@ -3528,23 +3526,23 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F104" s="5" t="str">
-        <f t="shared" ref="F104:F105" si="28">IF(B104="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" si="27"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G104" s="11" t="s">
         <v>51</v>
@@ -3553,23 +3551,23 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F105" s="5" t="str">
-        <f t="shared" si="28"/>
-        <v>ÅR</v>
+        <f t="shared" ref="F105:F108" si="30">IF(B105="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>51</v>
@@ -3578,23 +3576,23 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F106" s="5" t="str">
-        <f t="shared" ref="F106" si="29">IF(B106="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" si="30"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G106" s="11" t="s">
         <v>51</v>
@@ -3603,7 +3601,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>17</v>
@@ -3612,13 +3610,13 @@
         <v>18</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F107" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="F107" si="31">IF(B107="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G107" s="11" t="s">
@@ -3631,19 +3629,19 @@
         <v>13</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F108" s="5" t="str">
-        <f t="shared" ref="F108:F111" si="30">IF(B108="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="30"/>
         <v>KVARTAL</v>
       </c>
       <c r="G108" s="11" t="s">
@@ -3656,19 +3654,19 @@
         <v>13</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F109" s="5" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="F109:F127" si="32">IF(B109="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G109" s="11" t="s">
@@ -3678,22 +3676,22 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A110" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F110" s="5" t="str">
-        <f t="shared" ref="F110" si="31">IF(B110="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="32"/>
         <v>KVARTAL</v>
       </c>
       <c r="G110" s="11" t="s">
@@ -3703,7 +3701,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A111" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>18</v>
@@ -3712,13 +3710,13 @@
         <v>19</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F111" s="5" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="F111" si="33">IF(B111="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G111" s="11" t="s">
@@ -3731,19 +3729,19 @@
         <v>13</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F112" s="5" t="str">
-        <f t="shared" ref="F112:F130" si="32">IF(B112="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="32"/>
         <v>KVARTAL</v>
       </c>
       <c r="G112" s="11" t="s">
@@ -3756,13 +3754,13 @@
         <v>13</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>47</v>
@@ -3778,22 +3776,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A114" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F114" s="5" t="str">
-        <f t="shared" ref="F114" si="33">IF(B114="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F114:F115" si="34">IF(B114="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G114" s="11" t="s">
@@ -3803,7 +3801,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A115" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>19</v>
@@ -3812,13 +3810,13 @@
         <v>20</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F115" s="5" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>KVARTAL</v>
       </c>
       <c r="G115" s="11" t="s">
@@ -3831,13 +3829,13 @@
         <v>13</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>47</v>
@@ -3856,19 +3854,19 @@
         <v>13</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F117" s="5" t="str">
-        <f t="shared" ref="F117:F118" si="34">IF(B117="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="32"/>
         <v>KVARTAL</v>
       </c>
       <c r="G117" s="11" t="s">
@@ -3878,22 +3876,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A118" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F118" s="5" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="F118:F119" si="35">IF(B118="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G118" s="11" t="s">
@@ -3903,7 +3901,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A119" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>20</v>
@@ -3912,13 +3910,13 @@
         <v>24</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F119" s="5" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>KVARTAL</v>
       </c>
       <c r="G119" s="11" t="s">
@@ -3931,20 +3929,20 @@
         <v>13</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F120" s="5" t="str">
         <f t="shared" si="32"/>
-        <v>KVARTAL</v>
+        <v>ÅR</v>
       </c>
       <c r="G120" s="11" t="s">
         <v>51</v>
@@ -3956,20 +3954,20 @@
         <v>13</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F121" s="5" t="str">
-        <f t="shared" ref="F121:F122" si="35">IF(B121="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F121:F123" si="36">IF(B121="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G121" s="11" t="s">
         <v>51</v>
@@ -3978,23 +3976,23 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A122" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F122" s="5" t="str">
-        <f t="shared" si="35"/>
-        <v>KVARTAL</v>
+        <f t="shared" si="36"/>
+        <v>ÅR</v>
       </c>
       <c r="G122" s="11" t="s">
         <v>51</v>
@@ -4009,7 +4007,7 @@
         <v>21</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>7</v>
@@ -4018,7 +4016,7 @@
         <v>47</v>
       </c>
       <c r="F123" s="5" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>ÅR</v>
       </c>
       <c r="G123" s="11" t="s">
@@ -4034,16 +4032,16 @@
         <v>21</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F124" s="5" t="str">
-        <f t="shared" ref="F124:F126" si="36">IF(B124="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F124" si="37">IF(B124="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G124" s="11" t="s">
@@ -4059,16 +4057,16 @@
         <v>21</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F125" s="5" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="F125" si="38">IF(B125="2024","ÅR","KVARTAL")</f>
         <v>ÅR</v>
       </c>
       <c r="G125" s="11" t="s">
@@ -4081,20 +4079,20 @@
         <v>13</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F126" s="5" t="str">
-        <f t="shared" si="36"/>
-        <v>ÅR</v>
+        <f t="shared" si="32"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G126" s="11" t="s">
         <v>51</v>
@@ -4109,16 +4107,16 @@
         <v>21</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F127" s="5" t="str">
-        <f t="shared" ref="F127" si="37">IF(B127="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="32"/>
         <v>ÅR</v>
       </c>
       <c r="G127" s="11" t="s">
@@ -4131,20 +4129,20 @@
         <v>13</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F128" s="5" t="str">
-        <f t="shared" ref="F128" si="38">IF(B128="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
+        <f t="shared" ref="F128:F130" si="39">IF(B128="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
       </c>
       <c r="G128" s="11" t="s">
         <v>51</v>
@@ -4156,45 +4154,48 @@
         <v>13</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F129" s="5" t="str">
-        <f t="shared" si="32"/>
-        <v>KVARTAL</v>
+        <f t="shared" si="39"/>
+        <v>ÅR</v>
       </c>
       <c r="G129" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H129" s="11"/>
+      <c r="I129" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A130" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F130" s="5" t="str">
-        <f t="shared" si="32"/>
-        <v>ÅR</v>
+        <f t="shared" si="39"/>
+        <v>KVARTAL</v>
       </c>
       <c r="G130" s="11" t="s">
         <v>51</v>
@@ -4203,181 +4204,181 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A131" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F131" s="5" t="str">
-        <f t="shared" ref="F131:F133" si="39">IF(B131="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F131" si="40">IF(B131="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G131" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H131" s="11"/>
+      <c r="I131" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A132" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F132" s="5" t="str">
-        <f t="shared" si="39"/>
-        <v>ÅR</v>
+        <f t="shared" ref="F132:F136" si="41">IF(B132="2024","ÅR","KVARTAL")</f>
+        <v>KVARTAL</v>
       </c>
       <c r="G132" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H132" s="11"/>
-      <c r="I132" s="1" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A133" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F133" s="5" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="F133" si="42">IF(B133="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G133" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H133" s="11"/>
+      <c r="I133" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A134" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F134" s="5" t="str">
-        <f t="shared" ref="F134" si="40">IF(B134="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="41"/>
         <v>KVARTAL</v>
       </c>
       <c r="G134" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H134" s="11"/>
-      <c r="I134" s="1" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A135" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F135" s="5" t="str">
-        <f t="shared" ref="F135:F139" si="41">IF(B135="2024","ÅR","KVARTAL")</f>
+        <f t="shared" ref="F135" si="43">IF(B135="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G135" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H135" s="11"/>
+      <c r="I135" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A136" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F136" s="5" t="str">
-        <f t="shared" ref="F136" si="42">IF(B136="2024","ÅR","KVARTAL")</f>
+        <f t="shared" si="41"/>
         <v>KVARTAL</v>
       </c>
       <c r="G136" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H136" s="11"/>
-      <c r="I136" s="1" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A137" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F137" s="5" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="F137" si="44">IF(B137="2024","ÅR","KVARTAL")</f>
         <v>KVARTAL</v>
       </c>
       <c r="G137" s="11" t="s">
@@ -4390,102 +4391,48 @@
         <v>14</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F138" s="5" t="str">
-        <f t="shared" ref="F138" si="43">IF(B138="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
+        <f t="shared" ref="F138:F191" si="45">IF(B138="2024","ÅR","KVARTAL")</f>
+        <v>ÅR</v>
       </c>
       <c r="G138" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H138" s="11"/>
-      <c r="I138" s="1" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A139" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F139" s="5" t="str">
-        <f t="shared" si="41"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G139" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f t="shared" si="45"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G139" s="11"/>
       <c r="H139" s="11"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A140" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F140" s="5" t="str">
-        <f t="shared" ref="F140" si="44">IF(B140="2024","ÅR","KVARTAL")</f>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G140" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f t="shared" si="45"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G140" s="11"/>
       <c r="H140" s="11"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A141" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="F141" s="5" t="str">
-        <f t="shared" ref="F141:F194" si="45">IF(B141="2024","ÅR","KVARTAL")</f>
-        <v>ÅR</v>
-      </c>
-      <c r="G141" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f t="shared" si="45"/>
+        <v>KVARTAL</v>
+      </c>
+      <c r="G141" s="11"/>
       <c r="H141" s="11"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.4">
@@ -4888,32 +4835,8 @@
       <c r="G191" s="11"/>
       <c r="H191" s="11"/>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F192" s="5" t="str">
-        <f t="shared" si="45"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G192" s="11"/>
-      <c r="H192" s="11"/>
-    </row>
-    <row r="193" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F193" s="5" t="str">
-        <f t="shared" si="45"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G193" s="11"/>
-      <c r="H193" s="11"/>
-    </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F194" s="5" t="str">
-        <f t="shared" si="45"/>
-        <v>KVARTAL</v>
-      </c>
-      <c r="G194" s="11"/>
-      <c r="H194" s="11"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I193" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}"/>
+  <autoFilter ref="A1:I190" xr:uid="{BD17CB8A-0B79-4900-9C11-CBE12EAD6DD0}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -4923,25 +4846,25 @@
           <x14:formula1>
             <xm:f>LISTER!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D194 A2:A194</xm:sqref>
+          <xm:sqref>A2:A191 D2:D191</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{424D03F4-B91D-4C98-9865-9386CE07D412}">
           <x14:formula1>
             <xm:f>LISTER!$C$2:$C$13</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C194</xm:sqref>
+          <xm:sqref>C2:C191</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C0FD7FC9-0A01-4E4D-963C-4616ACB0FCFE}">
           <x14:formula1>
             <xm:f>LISTER!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E194</xm:sqref>
+          <xm:sqref>E2:E191</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8A352F04-E99B-434A-B2F4-238791E4E11C}">
           <x14:formula1>
             <xm:f>LISTER!$B$2:$B$9</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B194</xm:sqref>
+          <xm:sqref>B2:B191</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
